--- a/final_data_pipeline/output/311942longform.xlsx
+++ b/final_data_pipeline/output/311942longform.xlsx
@@ -753,7 +753,7 @@
         <v>63</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -842,7 +842,7 @@
         <v>63</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -931,7 +931,7 @@
         <v>63</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB4">
         <v>8000</v>
@@ -1020,7 +1020,7 @@
         <v>63</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB5">
         <v>8000</v>
@@ -1115,7 +1115,7 @@
         <v>63</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB6">
         <v>8000</v>
@@ -1210,7 +1210,7 @@
         <v>63</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB7">
         <v>8000</v>
@@ -1305,7 +1305,7 @@
         <v>63</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB8">
         <v>8000</v>
@@ -1394,7 +1394,7 @@
         <v>63</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB9">
         <v>8000</v>
@@ -1489,7 +1489,7 @@
         <v>63</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB10">
         <v>8000</v>
@@ -1578,7 +1578,7 @@
         <v>63</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB11">
         <v>8000</v>
@@ -1673,7 +1673,7 @@
         <v>63</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -1762,7 +1762,7 @@
         <v>63</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -2409,7 +2409,7 @@
         <v>63</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB20">
         <v>8000</v>
@@ -2504,7 +2504,7 @@
         <v>63</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB21">
         <v>8000</v>
@@ -2593,7 +2593,7 @@
         <v>63</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB22">
         <v>8000</v>
@@ -2682,7 +2682,7 @@
         <v>63</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB23">
         <v>8000</v>
@@ -2777,7 +2777,7 @@
         <v>63</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB24">
         <v>8000</v>
@@ -2872,7 +2872,7 @@
         <v>63</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB25">
         <v>8000</v>
